--- a/Assets/Game_Design/게임 시스템 기획서.xlsx
+++ b/Assets/Game_Design/게임 시스템 기획서.xlsx
@@ -143,7 +143,7 @@
     <t>스토리 보상</t>
   </si>
   <si>
-    <t>컷신, 은신처 대화, 다음 스테이지 해금</t>
+    <t>스토리씬, 은신처 대화, 다음 스테이지 해금</t>
   </si>
   <si>
     <t>목표 제압 성공</t>
@@ -433,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -511,6 +511,9 @@
     </xf>
     <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -3048,7 +3051,7 @@
       <c r="A3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C3" s="21" t="s">
@@ -3062,7 +3065,7 @@
       <c r="A4" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="27" t="s">
         <v>45</v>
       </c>
       <c r="C4" s="19" t="s">
@@ -3090,10 +3093,10 @@
       <c r="A6" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="28" t="s">
         <v>54</v>
       </c>
       <c r="D6" s="11" t="s">
